--- a/DSA_task_tracker_sheet/Copy of DSA_Task_Tracker.xlsx
+++ b/DSA_task_tracker_sheet/Copy of DSA_Task_Tracker.xlsx
@@ -1,33 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DSA-with-Java\DSA_task_tracker_sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D945944D-1AA6-4A00-B248-6D9AA230FD80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B95531-C2E3-497A-B2AC-E57522DF4349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Leetcode_Imp_Problems" sheetId="1" r:id="rId1"/>
     <sheet name="Zoho_Problems_List" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -1449,10 +1438,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>23</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1</c:v>
@@ -3798,11 +3787,11 @@
       </c>
       <c r="K2" s="11">
         <f>COUNTIF(Table1_3[Status],"Completed")</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" s="11">
         <f>COUNTIF(Table1_3[Status],"Pending")</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M2" s="11">
         <f>COUNTIF(Table1_3[Status],"In Progress")</f>
@@ -4288,7 +4277,7 @@
         <v>111</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G29" s="2"/>
       <c r="I29" s="1"/>
